--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AB6109B-4B19-40BA-A01F-92D6D664BC03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C3047E-3ED7-4EED-8E70-FA16FC246EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="3040" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="update" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>22nd August 2026</t>
+    <t>11th September 2026</t>
   </si>
 </sst>
 </file>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C3047E-3ED7-4EED-8E70-FA16FC246EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6008AF7D-32CA-40C5-9797-BB78BD91A457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="update" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>11th September 2026</t>
+    <t>24th September 2026</t>
   </si>
 </sst>
 </file>
@@ -833,14 +833,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>

--- a/data/update.xlsx
+++ b/data/update.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\kasparrufibach\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6008AF7D-32CA-40C5-9797-BB78BD91A457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E9F275-95E9-467F-AB61-F2FE57AD13EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>24th September 2026</t>
+    <t>19th October 2026</t>
   </si>
 </sst>
 </file>
